--- a/Heat transition tipping pathways/_heating_system_data.xlsx
+++ b/Heat transition tipping pathways/_heating_system_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naudl\Documents\GitHub\Heat_transition_tipping_pathways\Heat transition tipping pathways\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E058C29-9F08-4902-B7B3-04341DC31C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11EE28C-1154-4648-B53D-84AF4C618FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3384" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{F2133ED2-96E7-4F18-A093-754F4E711694}"/>
   </bookViews>
@@ -1044,7 +1044,7 @@
         <v>0.03</v>
       </c>
       <c r="N6" s="1">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="O6" t="s">
         <v>19</v>
